--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Commercial IT Sr. Data Solution Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7230c31a417de52</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=a7230c31a417de52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b652d7f75551953a</t>
+          <t>https://www.indeed.com/viewjob?jk=7eca245ea2227b61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd611d279ec668f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,137 +1091,137 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, Tableau, MLOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,137 +1546,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf96be74f55a1423</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea92df4da5f1755</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Scientific Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exact Sciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e296f6f6df9014b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, SQL Server, Data Modeling, ELT, MLOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ac56bcba1f58c59</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Scala, ETL, Tableau, MLOps, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a7cc0e0aaef8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-2</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Product Engineer (Software/Java)</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8d03326caca3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tech - Data Base Administrator</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gatik</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d9bc4d5f884e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Automation developer-2</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d46e8f60dd86848</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realtime Clinical Trial Management Systems</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,19 +3366,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3387,11 +3387,11 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,40 +3471,1965 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Data Architect, Data Foundry</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer (ETL)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Radial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Advisor - Data Architect, Data Foundry</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Kafka Streaming Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Marketing Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ATG Entertainment</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MarketDial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Barnes &amp; Thornburg LLP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Mike Albert Leasing, Inc</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Bizops Engineer-2</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Product Engineer (Software/Java)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Security and IT Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ProVation</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Engineer (ETL)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Radial</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, Scala, ETL, Tableau, MLOps, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c9a7cc0e0aaef8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>People Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tech - Data Base Administrator</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior AI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AliCloud DevOps Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect / Developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Navteca</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PAR Technology</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Azure Databricks Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Claritas Rx</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr Automation developer-2</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d46e8f60dd86848</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2 - Front-End</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SR SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Dollar General</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Goodlettsville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SQL Database Architect</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GSK Solutions</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Township of Hamilton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Integration Services Developer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AWS SageMaker Data Scientist</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bird Rides</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Cloud DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Liminal</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AWS Developer / Administrator</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ESYSTEMS, INC</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Realtime Clinical Trial Management Systems</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Invu Technology</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Applications Engineer, Full Stack - People</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Great Gray Trust Company</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>SAP Security Administrator</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>NJ, US USA</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D143" t="n">
         <v>10.4</v>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,55 +473,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5ffe3e0696e29a</t>
+          <t>https://www.indeed.com/viewjob?jk=008b82df0092f214</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Commercial IT Sr. Data Solution Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b82df0092f214</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Commercial IT Sr. Data Solution Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
+          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
+          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5075132839604a</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Everhealth – Senior Data Engineer (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1494c02a420f7168</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,69 +3636,69 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=9c10613312eae7d7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-2</t>
+          <t>Security and IT Systems Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
+          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Product Engineer (Software/Java)</t>
+          <t>Senior Bizops Engineer-2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
+          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Security and IT Systems Analyst</t>
+          <t>Senior Product Engineer (Software/Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
+          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Tech - Data Base Administrator</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Tech - Data Base Administrator</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Automation developer-2</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d46e8f60dd86848</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4878,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,19 +4906,19 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4927,11 +4927,11 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Power BI, Terraform, Bitbucket</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Realtime Clinical Trial Management Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Realtime Clinical Trial Management Systems</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,17 +5421,122 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Applications Engineer, Full Stack - People</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2813,12 +2813,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API/Integration Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc0dacaf9a9f3d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CooperCompanies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Henrietta, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=831952137ebf7901</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53773d34b99af77</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,104 +3636,104 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c10613312eae7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=9c10613312eae7d7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Security and IT Systems Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-2</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
+          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Product Engineer (Software/Java)</t>
+          <t>Security and IT Systems Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
+          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Bizops Engineer-2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Product Engineer (Software/Java)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Tech - Data Base Administrator</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Tech - Data Base Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
         </is>
       </c>
     </row>
@@ -4773,17 +4773,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Power BI, Terraform, Bitbucket</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Power BI, Terraform, Bitbucket</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realtime Clinical Trial Management Systems</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Realtime Clinical Trial Management Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
@@ -5473,17 +5473,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,15 +5526,260 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2813,12 +2813,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>API/Integration Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc0dacaf9a9f3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API/Integration Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Capio Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc0dacaf9a9f3d3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CooperCompanies</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Henrietta, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5402734548997ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=831952137ebf7901</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=831952137ebf7901</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Bizops Engineer-2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6821b6da5b7382e0</t>
+          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Security and IT Systems Analyst</t>
+          <t>Senior Product Engineer (Software/Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
+          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Security and IT Systems Analyst</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>ProVation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Scala, ETL, Tableau, MLOps, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a7cc0e0aaef8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-2</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, Scala, ETL, Tableau, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a7cc0e0aaef8e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Product Engineer (Software/Java)</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Tech - Data Base Administrator</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Tech - Data Base Administrator</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,19 +4976,19 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4997,11 +4997,11 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Power BI, Terraform, Bitbucket</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Realtime Clinical Trial Management Systems</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git, SQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1511699a4fb38068</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Power BI, Terraform, Bitbucket</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,77 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Agentic and Generative Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Xsolis</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7230c31a417de52</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eca245ea2227b61</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd611d279ec668f</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65534676e608624f</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>API/Integration Developer</t>
+          <t>Python/PySpark Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc0dacaf9a9f3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=831952137ebf7901</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Customertimes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Poland, ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b92e49b2282be9b0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,59 +3681,59 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c10613312eae7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Bizops Engineer-2</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07739c1bad763116</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Product Engineer (Software/Java)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, ELT, Jenkins, Maven, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ad51a285cdcb71</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Security and IT Systems Analyst</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ProVation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b47e577ffd7e5fa</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Scala, ETL, Tableau, MLOps, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a7cc0e0aaef8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,49 +4311,49 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tech - Data Base Administrator</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, Azure Cosmos DB, Data Modeling, ETL, CI/CD</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3fa1c25dd9c540</t>
+          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,42 +4581,42 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, PostgreSQL, DynamoDB, ETL, Tableau</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,54 +4661,54 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,67 +4801,67 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Power BI, Terraform, Bitbucket</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5360,356 +5360,6 @@
         </is>
       </c>
       <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Applications Engineer, Full Stack - People</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Great Gray Trust Company</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Agentic and Generative Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Xsolis</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,42 +783,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer III - Admin Center</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f33f4a77a6827e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,52 +976,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,69 +2726,69 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Python/PySpark Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f909cb7ec3483</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,42 +4581,42 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,59 +4661,59 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,15 +5351,120 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1be1c6c3f58391</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
+          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
+          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,69 +4651,69 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
@@ -5368,17 +5368,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,15 +5456,50 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>HRIS Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=087b0e02bfb3bda8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,69 +2761,69 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Customertimes</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark, PySpark</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92e49b2282be9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Customertimes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Poland, ME, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=b92e49b2282be9b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>IXIS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
+          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Integration Services Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,69 +4651,69 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
@@ -4913,17 +4913,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Architect- Amazon Connect SME</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=0f52900a5482cbc6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
         </is>
       </c>
     </row>
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SAP Security Administrator</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,15 +5491,50 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HRIS Solution Architect</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087b0e02bfb3bda8</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,69 +2761,69 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Snowflake Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
+          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,84 +776,84 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Admin Center</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f33f4a77a6827e</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer III - Admin Center</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f33f4a77a6827e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Snowflake Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41da8b7d34b4e71d</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect (Remote)</t>
+          <t>Test Analyst - ETL QA Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Panacea Direct Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2897,73 +2897,73 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Customertimes</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Poland, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
+          <t>https://www.indeed.com/viewjob?jk=b92e49b2282be9b0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Customertimes</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92e49b2282be9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IXIS</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, NoSQL, Data Modeling, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,49 +3436,49 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Sr Software Engineer - Live and Linear Tooling</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3492,73 +3492,73 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=3813402781f4a5a6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, Tableau</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Java Development Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=044788dae086d6fb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,42 +4616,42 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Integration Services Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, ETL, Jenkins, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,59 +4661,59 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947ca7824810f0d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, ETL, GitHub Actions, Git, Bitbucket, SQL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=75d9a983054dd1ae</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4878,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Application Architect- Amazon Connect SME</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f52900a5482cbc6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Application Architect- Amazon Connect SME</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f52900a5482cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90e3ab65ff267d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5465,76 +5465,6 @@
         </is>
       </c>
       <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Guidewire Architect</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Admin Center</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f33f4a77a6827e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,87 +941,87 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,104 +2691,104 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,69 +2831,69 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Test Analyst - ETL QA Engineer</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Panacea Direct Inc</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e33833632ced64</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Customertimes</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland, ME, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92e49b2282be9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Google Cloud Platform, GCP, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Live and Linear Tooling</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3813402781f4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddbc0db8e0ab6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae67cbf3ff6a6b12</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656f4be308d712a</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Kafka, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807cc7dc8b72ea8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,102 +3681,102 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3807,11 +3807,11 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0e71df61def4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Development Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=044788dae086d6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,42 +4266,42 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,59 +4591,59 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, MySQL, Data Modeling, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, ETL, GitHub Actions, Git, Bitbucket, SQL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d9a983054dd1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Application Architect- Amazon Connect SME</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f52900a5482cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>SAP Security Administrator</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5045,426 +5045,6 @@
         </is>
       </c>
       <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Agentic and Generative Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Xsolis</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>ETL Developer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>United Nations Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Guidewire Architect</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Guidewire Architect</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0411e0606d3713</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Sr. Site Reliability Engineer (Database focused)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb7e7177646b9e8</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c672c58481ff2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, SQS, SNS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa2def71f96f681</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Full Stack Engineer – SaaS Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436d97d6edae9756</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,69 +4231,69 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
@@ -4976,77 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Guidewire Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>SAP Security Administrator</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=744aa8787fc16632</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb7e7177646b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,69 +2831,69 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka, MySQL, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,29 +3741,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – SaaS Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Engineer – SaaS Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,42 +4231,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3aa60883fb8d23</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Database Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>GSK Solutions</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,59 +4416,59 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Senior Engineer (.NET/React)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,15 +4966,190 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>App Dev &amp; Support Engineer III</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Conduent</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ETL Developer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>United Nations Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,104 +2866,104 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Operations Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Hadoop, Hive, Sqoop, HBase, Spark, Snowflake, Snow Pipe, Time Travel</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,77 +3286,77 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca0a83288d9224</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,94 +3636,94 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,25 +3733,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – SaaS Platform</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Full Stack Engineer – SaaS Platform</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SQL Database Architect</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GSK Solutions</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86692750669aac55</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,139 +4441,139 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27acae47fa052436</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,29 +4581,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer (.NET/React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, SQL Server, PostgreSQL, MySQL, ETL, Docker, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61df1a30908c512a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Guidewire Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
         </is>
       </c>
     </row>
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,52 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,77 +713,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Database focused)</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c426f94a2eb5de</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,29 +2901,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Operations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior, Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>ATG Entertainment</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,84 +3786,84 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,25 +3873,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1547f58f63e5ddbf</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server, Kimball, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0623688c68382c</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – SaaS Platform</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,29 +4371,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Full Stack Engineer – SaaS Platform</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
@@ -4563,60 +4563,60 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,59 +4626,59 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Invu Technology</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,157 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ETL Developer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>United Nations Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Data Factory, Scala, Oracle, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer - Fullstack</t>
+          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior, Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
@@ -3513,52 +3513,52 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Sr Software Development Engineer - Hasbro Direct</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Hasbro, Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=59aa493bfb3826f0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Python Software Engineer - Schaumburg, IL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,94 +3881,94 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,42 +3978,42 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – SaaS Platform</t>
+          <t>AliCloud DevOps Senior Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Full Stack Engineer – SaaS Platform</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,174 +4651,174 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Invu Technology</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Hadoop, Spark, Scala, NoSQL, Terraform, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a735e4ae41782f65</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suntex Marina Investors, LLC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, PySpark, Scala, Polars, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=edce04084d1da5d6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Architect - Amazon Connect SME</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=65acf5a8c014e9c7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Microsoft Dynamics 365 Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=59479444c6517572</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5088,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,17 +5316,192 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>App Dev &amp; Support Engineer III</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Conduent</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Slip Robotics</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Agentic and Generative Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Xsolis</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,130 +503,130 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Commercial IT Sr. Data Solution Developer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
+          <t>https://www.indeed.com/viewjob?jk=5af157c666d12c35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Commercial IT Sr. Data Solution Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ebd75b55c0b878</t>
+          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83cf0ba40f1b8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IS Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CareOregon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Engineering Instructor</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, Databricks, Hadoop, Spark, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=dc8cc5c5ed045642</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
+          <t>Operations Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
+          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer - Fullstack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
+          <t>https://www.indeed.com/viewjob?jk=3781603622dffbfd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior, Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ATG Entertainment</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b060fca7c8f1c27c</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,77 +3531,77 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c974247907065262</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Hasbro Direct</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hasbro, Inc.</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59aa493bfb3826f0</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Schaumburg, IL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Sr Software Development Engineer - Hasbro Direct</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Hasbro, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,19 +3856,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=59aa493bfb3826f0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Python Software Engineer - Schaumburg, IL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Data Modeling, MLOps, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=b80993c7486f0a43</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,94 +3986,94 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,42 +4083,42 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7828253d03dda8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AliCloud DevOps Senior Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be416b224d94d78</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Suntex Marina Investors, LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, PySpark, Scala, Polars, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=edce04084d1da5d6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – SaaS Platform</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Suntex Marina Investors, LLC</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,69 +4791,69 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, PySpark, Scala, Polars, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edce04084d1da5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Application Architect - Amazon Connect SME</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,19 +4906,19 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65acf5a8c014e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics 365 Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>ESYSTEMS, INC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59479444c6517572</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d748d1785eb240</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Application Architect - Amazon Connect SME</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=65acf5a8c014e9c7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Microsoft Dynamics 365 Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=59479444c6517572</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Guidewire Architect</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
@@ -5502,6 +5502,111 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ETL Developer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>United Nations Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guidewire Architect</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,157 +468,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b82df0092f214</t>
+          <t>https://www.indeed.com/viewjob?jk=5af157c666d12c35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Commercial IT Sr. Data Solution Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af157c666d12c35</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Commercial IT Sr. Data Solution Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
+          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,174 +836,174 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IS Data Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CareOregon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. PS Sales Solutions Architect</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineering Instructor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Athena, Databricks, Hadoop, Spark, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=dc8cc5c5ed045642</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,112 +2586,112 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering Instructor</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, Databricks, Hadoop, Spark, ETL, ELT, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc8cc5c5ed045642</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Operations Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
+          <t>https://www.indeed.com/viewjob?jk=3781603622dffbfd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Senior, Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3781603622dffbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
+          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
+          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer - Fullstack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Sr Software Development Engineer - Hasbro Direct</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hasbro, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=59aa493bfb3826f0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Data Modeling, MLOps, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b80993c7486f0a43</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Hasbro Direct</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hasbro, Inc.</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,19 +3856,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59aa493bfb3826f0</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Schaumburg, IL</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Data Modeling, MLOps, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80993c7486f0a43</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Python Software Engineer - Schaumburg, IL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,59 +4021,59 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,42 +4083,42 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Web Developer (with DevOps/SRE Experience)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>SOLUTION INNOVATORS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>South Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=7af5fd68caec2af9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suntex Marina Investors, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, PySpark, Scala, Polars, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=edce04084d1da5d6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Development Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Suntex Marina Investors, LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, PySpark, Scala, Polars, Data Modeling, ETL, ELT</t>
+          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edce04084d1da5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=044788dae086d6fb</t>
         </is>
       </c>
     </row>
@@ -4703,17 +4703,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,42 +4826,42 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8cdbdda0b386a7</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ESYSTEMS, INC</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Application Architect - Amazon Connect SME</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,29 +4966,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d748d1785eb240</t>
+          <t>https://www.indeed.com/viewjob?jk=65acf5a8c014e9c7</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Application Architect - Amazon Connect SME</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65acf5a8c014e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics 365 Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59479444c6517572</t>
+          <t>https://www.indeed.com/viewjob?jk=99977a748ac9e602</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,29 +5071,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Microsoft Dynamics 365 Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=59479444c6517572</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Applications Engineer, Full Stack - People</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applications Engineer, Full Stack - People</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
+          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Agentic and Generative Data Scientist II</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Xsolis</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,77 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Guidewire Architect</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6691046f35802016</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Guidewire Architect</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc489e180f6f4e8</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-19.xlsx
+++ b/results/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Commercial IT Sr. Data Solution Developer</t>
+          <t>Associate Data Engineer- Hyperscale- Cloud</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
+          <t>https://www.indeed.com/viewjob?jk=eee1c6c65c9ef5f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Commercial IT Sr. Data Solution Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Angeion Group, LLC</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99d5e0e955f545</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SAP Data Migration Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e72c1940ea5774f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Angeion Group, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, SQS, API Gateway, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=33e99b8f9b3b2740</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Solutions Architect</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>California State University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IS Data Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CareOregon</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Senior Data Analytics Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>California State University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,129 +881,129 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=1f09549d52039954</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
+          <t>https://www.indeed.com/viewjob?jk=27af40b4286641bb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
+          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Analyst</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=99004f0ccb75bff8</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b800e1dd513c62b0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
+          <t>https://www.indeed.com/viewjob?jk=67db4676545517dc</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
+          <t>https://www.indeed.com/viewjob?jk=465e4cfb02687a43</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=86bf9595c61e4e9b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
+          <t>https://www.indeed.com/viewjob?jk=172ac3f4d79041c0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
+          <t>https://www.indeed.com/viewjob?jk=24d19bd6c4e70f90</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8c07b3c7931842</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
+          <t>https://www.indeed.com/viewjob?jk=958277eca165b7b0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb652fefd41a30</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fec5ae34e47340c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
+          <t>https://www.indeed.com/viewjob?jk=d917504603bf084e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
+          <t>https://www.indeed.com/viewjob?jk=39e24f6a7ce5748f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
+          <t>https://www.indeed.com/viewjob?jk=5524c8ba85bcff30</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c50acddb7517f2d4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
+          <t>https://www.indeed.com/viewjob?jk=82e9fffb45114190</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb7b8041bb03853</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c2e5757b692357</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4f14f3bff02b38d0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
+          <t>https://www.indeed.com/viewjob?jk=150a62779e64cf28</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
+          <t>https://www.indeed.com/viewjob?jk=d491b10b83c519d4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9b3b6bd775a2d2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
+          <t>https://www.indeed.com/viewjob?jk=b74d7177a759a3cb</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
+          <t>https://www.indeed.com/viewjob?jk=c0185fa4b3994bde</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaa4bd12cb8e36e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f7162a38c502a046</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d4bc09ac9bd67f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
+          <t>https://www.indeed.com/viewjob?jk=37f27536cfc96c94</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
+          <t>https://www.indeed.com/viewjob?jk=095644e54329e701</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94558aafefd5ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b89c32a876770ee</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
+          <t>https://www.indeed.com/viewjob?jk=2db2dd7c1e8f6377</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c9ee617abae433</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=be1719cac82392e0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
+          <t>https://www.indeed.com/viewjob?jk=43ee942f932f912d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=95181713ad4ed52c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ea68b4c4f16f8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e908cc2565c6ad0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
+          <t>https://www.indeed.com/viewjob?jk=d87a925620ad7f49</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
+          <t>https://www.indeed.com/viewjob?jk=f1660cec9806eccb</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
+          <t>https://www.indeed.com/viewjob?jk=d20789ddb9670a91</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4670a44a18b5d0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fbe0040faa9f86</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineering Instructor</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, Databricks, Hadoop, Spark, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc8cc5c5ed045642</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2b5a1a6ff87359</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,77 +2586,77 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
+          <t>https://www.indeed.com/viewjob?jk=8022de7456a51615</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Data Engineer - Project Delivery Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ee89a75146fdc182</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dca82b8d363fd2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ac32a158d5ead3ae</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=439f5cb6a23d1919</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c97b89e39037ee8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=b92ef16eb7915a5a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50742e69706ff73d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Engineering</t>
+          <t>Snowflake Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=f764dc94faa7a206</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Network Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Studio McGee</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>Senior Network Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3781603622dffbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=d82f40ea9ef1670c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Migration Architect (Microsoft Dynamics 365)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f58b7b1afbeec48</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer - Fullstack</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, SQL Server, MySQL, NoSQL, ETL, Jenkins, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
+          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solution Architect – Data, Analytics &amp; Microsoft Platform (Power BI, Power Apps, Fabric, Databricks)</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db3760b4023c14b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7d7e089523b996</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad728c60f5ddf1d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c76512f619110f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995099ed2a56911e</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,102 +3436,102 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8c4071e8f4f773</t>
+          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Spark, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b9e607fd2d0d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>MarketDial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8e657cbba2095</t>
+          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marketing Automation Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311cdc9cc020263</t>
+          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MarketDial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Polars, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc892ea3db24915</t>
+          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Barnes &amp; Thornburg LLP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794676769f713195</t>
+          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Governance Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83874b4efc59bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Barnes &amp; Thornburg LLP</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f399460ba9c2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer- Martech</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mike Albert Leasing, Inc</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b7173086c8af5c</t>
+          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Hasbro Direct</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hasbro, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59aa493bfb3826f0</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Information Technology</t>
+          <t>Data Governance Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer-Information Technology</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Data Modeling, MLOps, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80993c7486f0a43</t>
+          <t>https://www.indeed.com/viewjob?jk=07adf7cbff63a0bd</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>People Systems Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,42 +3846,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce7027a3a18e114</t>
+          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer- Martech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,84 +3891,84 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa39bb5af60e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec5aac03a88bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Governance Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5d1a6525d2d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>People Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,50 +3978,50 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f31b2374dfd81d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Schaumburg, IL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Professional, Data Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MVP Health Care</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0aebe8f122a069d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Data Modeling, Power BI, Tableau, Airflow, Python, SQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud - IT Resiliency Solutions - Remote</t>
+          <t>SaaS Platform-Full Stack Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Cloud Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f531126ad868d253</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90490552a1c9fe28</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Web Developer (with DevOps/SRE Experience)</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SOLUTION INNOVATORS</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af5fd68caec2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Suntex Marina Investors, LLC</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, PySpark, Scala, Polars, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edce04084d1da5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Java Development Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,77 +4511,77 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=044788dae086d6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Data Modeling, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Liminal</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,67 +4591,67 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SaaS Platform-Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Unity Catalog, Vertex AI, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9da75f20591aeee</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Azure Databricks Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hive, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,129 +4766,129 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1830746155036d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Applications Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Piermont Bank</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba52e4c7be1b38da</t>
+          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Machinify</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a2879bbf581653</t>
+          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Cloud/Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8cdbdda0b386a7</t>
+          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Slip Robotics</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102d918cc41c8445</t>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Liminal</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad05bfbb65cf4fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Application Architect - Amazon Connect SME</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65acf5a8c014e9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Agentic and Generative Data Scientist II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Xsolis</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, NoSQL, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99977a748ac9e602</t>
+          <t>https://www.indeed.com/viewjob?jk=8c98eb4ba04c2bce</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545fbf2f702616bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a186a80a6e332546</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics 365 Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59479444c6517572</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9313b15df56fe4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Piermont Bank</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Everett, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, NoSQL, ETL, Docker, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c910ffc54c4ad833</t>
+          <t>https://www.indeed.com/viewjob?jk=2998be2c78d17cd6</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Senior BI Consultant (Power BI) - 26-02719</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Machinify</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19f30d9595225fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2775cd0a4ba358b4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Blob Storage, Google Cloud Platform, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,322 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Applications Engineer, Full Stack - People</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=558f0e9f3952caf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0c3678726f7cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf2bd60b7775522</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e199cfaab686fcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaf29b51d053945</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0581c78c0e903b</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>ETL Developer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>United Nations Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, NoSQL, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b2c5f7604ecdfb50</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Support Engineer III</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52c6f68144e455b</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Agentic and Generative Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Xsolis</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, Snowflake, MLOps, MLflow, CI/CD, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98906d283f683359</t>
         </is>
       </c>
     </row>
